--- a/docs/TestCases/Test_Cases.xlsx
+++ b/docs/TestCases/Test_Cases.xlsx
@@ -9,7 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Tabelle1_2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="107">
   <si>
     <t xml:space="preserve">Demoblaze Test Cases</t>
   </si>
@@ -443,16 +443,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Leave  username field empty
+      <t xml:space="preserve">  Leave  username field empty
 </t>
     </r>
     <r>
@@ -540,6 +531,698 @@
   </si>
   <si>
     <t xml:space="preserve">Failed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Module 2 : Login/Logout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login with valid credentials </t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is not logged in and on the homepage</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click Log in
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Enter username
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Enter Password
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click Log in button</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged in and landed on home homepage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attempt login with non-existing credentials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username : random1199
+Password : random1199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User receives a „User does not exist.“ pop-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attempt login with empty username field</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click Log in
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Leave username field empty
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Enter Password
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click Log in button</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attempt login with empty password field</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click Log in 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Enter username
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Leave Password field empty
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click Log in button</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attempt login with valid username and invalid password</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Username : mrdimitrov1234
+Password : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">random1199</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">User receives a generic authentication error message that does not reveal whether the username or password is incorrect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User receives a „Wrong password.“ pop-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attempt login with invalid username and valid password</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Username : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">random1199
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Password : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">test1234</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attempt login with all empty fields</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click Log in 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">  Leave  username field empty
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Leave Password field empty
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click Log in button</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attempt login with only space characters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The application accepts whitespace-only credentials and grants an authenticated session. The navigation bar changes to logged-in state. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login with XSS payload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username :  &lt;script&gt;alert('test')&lt;/script&gt; 
+Password :  &lt;script&gt;alert('test')&lt;/script&gt; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input should be sanitized.
+Authentication should fail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The application accepts script-tag input as credentials and grants an authenticated session. The payload is displayed as the logged-in username.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logout by clicking the button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged in</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click Log out 
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged out and navigated to homepage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged out and landed on homepage for users not logged in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Logout button is visible after login</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Login with valid credentials </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Observe navigation bar
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Logout button is visible after successful login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Login button is visible after logout</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click Log out </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Observe navigation bar
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Login and Sign up buttons are visible again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged out and laned on the homepage</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click Log out 
+</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -549,7 +1232,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -581,12 +1264,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="16"/>
       <color theme="1"/>
@@ -608,6 +1285,7 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -616,6 +1294,39 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00A933"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC9211E"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -700,69 +1411,101 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -825,10 +1568,10 @@
       <rgbColor rgb="FF5983B0"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFC9211E"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -1017,668 +1760,668 @@
   <dimension ref="A1:W21"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="35.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="30.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="22.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="21.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="35.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="21.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="3" t="s">
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="5" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="7" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="9" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="11" t="s">
         <v>22</v>
       </c>
       <c r="N6" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="9" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="M7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="N7" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="9" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="L8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="N8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="9" t="s">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="L9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="N9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="9" t="s">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10" t="s">
+      <c r="J10" s="11"/>
+      <c r="K10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="M10" s="10" t="s">
+      <c r="M10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="N10" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="9" t="s">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="L11" s="12" t="s">
+      <c r="L11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="N11" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="264.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="9" t="s">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="L12" s="12" t="s">
+      <c r="L12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="M12" s="10" t="s">
+      <c r="M12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="10" t="s">
+      <c r="N12" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="9" t="s">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="L13" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M13" s="10" t="s">
+      <c r="M13" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N13" s="10" t="s">
+      <c r="N13" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="42.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1714,89 +2457,876 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:W25"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="27.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="23.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="35.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="21.14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O1" s="3"/>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="150.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="3"/>
+    <row r="1" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="80.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="89.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="51.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="78.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="60.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="65.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="J19" s="23"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="42.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="E3:N3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M6:M18" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N6:N18" type="list">
+      <formula1>"Not Run,Passed,Failed,Blocked"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" display=" https://www.demoblaze.com/"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter/>
   </headerFooter>
 </worksheet>
 </file>
--- a/docs/TestCases/Test_Cases.xlsx
+++ b/docs/TestCases/Test_Cases.xlsx
@@ -5,11 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Tabelle1_2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Registration" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Login Logout" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Product catalog" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Cart" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="187">
   <si>
     <t xml:space="preserve">Demoblaze Test Cases</t>
   </si>
@@ -849,26 +851,8 @@
     <t xml:space="preserve">Attempt login with valid username and invalid password</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Username : mrdimitrov1234
-Password : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">random1199</t>
-    </r>
+    <t xml:space="preserve">Username : mrdimitrov1234
+Password : random1199</t>
   </si>
   <si>
     <t xml:space="preserve">User receives a generic authentication error message that does not reveal whether the username or password is incorrect.</t>
@@ -883,45 +867,8 @@
     <t xml:space="preserve">Attempt login with invalid username and valid password</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Username : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">random1199
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Password : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">test1234</t>
-    </r>
+    <t xml:space="preserve">Username : random1199
+Password : test1234</t>
   </si>
   <si>
     <t xml:space="preserve">Log-07</t>
@@ -1223,6 +1170,527 @@
       <t xml:space="preserve">Click Log out 
 </t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Module 3: Product Catalog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">View Phones category 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged in and on the homepage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to categories sidebar
+2.Click Phones category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only products from the Phones category are listed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">View Laptops category
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to categories sidebar
+2.Click Laptops category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only products from the Laptops category are listed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">View Monitors category
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to categories sidebar
+2.Click Monitors category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only products from the Monitors category are listed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open product details 
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on any product</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">The user is redirected to the product page where the following things are clearly visible:
+-Image
+-Name
+-Price
+-Description
+-“Add to cart“ button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The user is redirected to the product page where the following things are clearly visible:
+-Name
+-Price
+-Description
+-“Add to cart“ button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify product image</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on any product</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Username : mrdimitrov1234
+Password : test1235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The images displayed before and after clicking on a product are identical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The images are identical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify product price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username : mrdimitrov1234
+Password : test1236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The prices displayed before and after clicking on a product are identical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The prices are identical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify product description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username : mrdimitrov1234
+Password : test1237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The descriptions displayed before and after clicking on a product are identical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The descriptions are identical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify navigation back to homepage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username : mrdimitrov1234
+Password : test1238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After opening any product page there is a clearly visible navigation button to go back to homepage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There is no visible navigation back button! 
+Users must use home button to return to home page!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify "Home" page displays all products</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Observe Home page
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Navigate to and click next button below the products
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Observe next page
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Repeat steps </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> until no more pages</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Username : mrdimitrov1234
+Password : test1239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products from all categories are displayed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch between categories multiple times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click on following categories in rapid succession:
+1.Phones 
+2.Laptops
+3. Monitors 
+4.Phones again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct products are displayed after each category switch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify product page URL changes when opening a product</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on first displayed product
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on second displayed product
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on any other displayed product</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Username : mrdimitrov1234
+Password : test1240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unique product page URL is loaded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unique product page URL is loaded. 
+(Product index is increasing based on position in grid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify no cross-category products are displayed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Open phones category</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Username : mrdimitrov1234
+Password : test1241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No laptop or monitor products are displayed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Module 4: Cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CART-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add single item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CART-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add multiple items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CART-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CART-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add duplicate item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CART-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cart persists after refresh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CART-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cart persists after logout/login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CART-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add item while not logged in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CART-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove all items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CART-09</t>
   </si>
 </sst>
 </file>
@@ -1232,7 +1700,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1311,12 +1779,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1327,6 +1789,7 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1411,7 +1874,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1488,24 +1951,28 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2497,7 +2964,7 @@
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2938,7 +3405,7 @@
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
     </row>
-    <row r="13" customFormat="false" ht="80.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -3006,7 +3473,7 @@
       <c r="J14" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="K14" s="22" t="s">
+      <c r="K14" s="11" t="s">
         <v>87</v>
       </c>
       <c r="L14" s="11" t="s">
@@ -3205,7 +3672,7 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
-      <c r="J19" s="23"/>
+      <c r="J19" s="22"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
@@ -3329,4 +3796,1452 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:W1048576"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="23.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="35.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="23.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="21.14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="70" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="79.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="85.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="113.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="35.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="35.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="54.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="57.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="109.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="93.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="78.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="60.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="J18" s="22"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="42.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+    </row>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="E3:N3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M6:M17" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N6:N17" type="list">
+      <formula1>"Not Run,Passed,Failed,Blocked"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" display=" https://www.demoblaze.com/"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:W1048576"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="35.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="21.14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="11"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="H10" s="11"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H12" s="11"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="89.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="J15" s="22"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="42.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="E3:N3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M6:M14" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N6:N14" type="list">
+      <formula1>"Not Run,Passed,Failed,Blocked"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" display=" https://www.demoblaze.com/"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/docs/TestCases/Test_Cases.xlsx
+++ b/docs/TestCases/Test_Cases.xlsx
@@ -5,13 +5,16 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Login Logout" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Login &amp; Logout" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Product catalog" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Cart" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Checkout &amp; Place Order" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Contact Form" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="About Us" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="301">
   <si>
     <t xml:space="preserve">Demoblaze Test Cases</t>
   </si>
@@ -1648,10 +1651,200 @@
     <t xml:space="preserve">Add single item</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on a product 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click add to cart
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on cart from navbar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Assert that correct product is added to cart</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">The chosen product is correctly added to the cart.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The correct product is added to cart.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CART-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Add multiple items</t>
+    <t xml:space="preserve">Add 3 different items</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on a product 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click add to cart
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Return to homepage and repeat steps 1 and 2 for a different product.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on cart from navbar</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">The chosen products are correctly added to the cart.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The correct products are added to the cart.</t>
   </si>
   <si>
     <t xml:space="preserve">CART-03</t>
@@ -1660,37 +1853,2071 @@
     <t xml:space="preserve">Remove item</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on a product 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click add to cart
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on cart from navbar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on „delete“ button</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">The product is removed from cart.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The product is removed from cart.
+Cart is left empty.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CART-04</t>
   </si>
   <si>
     <t xml:space="preserve">Add duplicate item</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on a product 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click add to cart
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Return to homepage and repeat steps 1 and 2 for the same product.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on cart from navbar</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple entries of the chosen product are correctly added to the cart.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CART-05</t>
   </si>
   <si>
     <t xml:space="preserve">Cart persists after refresh</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on a product 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click add to cart
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on cart from navbar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Refresh the page</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Product/s are still in cart.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Works when only one product is in the cart.
+Shuffles the places of different products.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CART-06</t>
   </si>
   <si>
     <t xml:space="preserve">Cart persists after logout/login</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on a product  
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click add to cart 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Return to homepage
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Repeat steps 1 and 2 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click logout button from navbar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click Login button again
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Use the same credentials as previous login
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on cart</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Works as intended.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CART-07</t>
   </si>
   <si>
     <t xml:space="preserve">Add item while not logged in</t>
   </si>
   <si>
+    <t xml:space="preserve">User is NOT logged in and on the homepage</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on a product 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click add to cart
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Login 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on cart</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">The chosen product is added to cart and visible after login.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The product in not transferred to the cart after login.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CART-08</t>
   </si>
   <si>
     <t xml:space="preserve">Remove all items</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on a product 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click add to cart
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Return to homepage and repeat for multiple products
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on cart from navbar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on „delete“ button for every product.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Products are correctly removed from the cart one by one and cart is left empty after last product is deleted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All products were removed successfully. Cart became empty.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CART-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify cart survives browser restart</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">  Click on a product 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click add to cart 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. Close browser
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Reopen same browser
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Navigate to Demoblaze website
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Log in
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on cart from navbar</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Username : mrdimitrov1234
+Password : test1242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previously added products remain in the cart after browser restart.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Module 5: Checkout / Place Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place order with valid data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged in, has 1 product added to cart and navigated to cart page.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on Place order button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Fill out form with valid dummy credentials
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on purchase</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dummy test-purchase credentials:
+Name: Martin Dimitrov 
+Country: Switzerland 
+City: Pontresina 
+Credit Card: 4444111155559999 
+Month: 12 
+Year: 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order is successfully placed and confirmation message is displayed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order is successfully placed and confirmation message is displayed.
+User is provided with Order ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place order with empty cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged in, has NO product added to cart and navigated to cart page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is displayed an error message or a pop-up stating that the cart is currently empty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A success message “Thank you for your purchase!” appears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place order with empty Name field</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on Place order button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Fill out form with valid dummy credentials leaving Name field empty
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on purchase</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dummy test-purchase credentials:
+Country: Switzerland 
+City: Pontresina 
+Credit Card: 4444111155559999 
+Month: 12 
+Year: 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is displayed an error message or a pop-up stating that all fields need to be filled to complete purchase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is displayed a pop-up stating : 
+“Please fill out Name and Creditcard.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place order with empty Country field</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on Place order button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Fill out form with valid dummy credentials leaving Country field empty
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on purchase</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dummy test-purchase credentials:
+Name: Martin Dimitrov 
+City: Pontresina 
+Credit Card: 4444111155559999 
+Month: 12 
+Year: 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place order with empty City field</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on Place order button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Fill out form with valid dummy credentials leaving City field empty
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on purchase</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dummy test-purchase credentials:
+Name: Martin Dimitrov 
+Country: Switzerland 
+Credit Card: 4444111155559999 
+Month: 12 
+Year: 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place order with empty Credit Card field</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on Place order button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Fill out form with valid dummy credentials leaving Credit Card field empty
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on purchase</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dummy test-purchase credentials:
+Name: Martin Dimitrov 
+Country: Switzerland 
+City: Pontresina 
+Month: 12 
+Year: 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is diplayed a pop-up stating : 
+“Please fill out Name and Creditcard.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place order with empty Month field</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on Place order button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Fill out form with valid dummy credentials leaving Month field empty
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on purchase</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dummy test-purchase credentials:
+Name: Martin Dimitrov 
+Country: Switzerland 
+City: Pontresina 
+Credit Card: 4444111155559999 
+Year: 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place order with empty Year field</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on Place order button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Fill out form with valid dummy credentials leaving Year field empty
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on purchase</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dummy test-purchase credentials:
+Name: Martin Dimitrov 
+Country: Switzerland 
+City: Pontresina 
+Credit Card: 4444111155559999 
+Month: 12 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place order with ALL empty fields</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on Place order button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Leave entire form empty
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on purchase</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place order with letters in Credit Card field</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on Place order button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Fill out Credit Card field with letters
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Fill the rest of the fields with valid credentials
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on purchase</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dummy test-purchase credentials:
+Name: Martin Dimitrov 
+Country: Switzerland 
+City: Pontresina 
+Credit Card: AAAABBBBCCCCDDDD 
+Month: 12 
+Year: 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is displayed an error message or a pop-up stating that one or more fields have invalid data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place order with expired card date</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on Place order button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Fill out form with provided dummy credentials
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on purchase</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dummy test-purchase credentials:
+Name: Martin Dimitrov 
+Country: Switzerland 
+City: Pontresina 
+Credit Card: 4444111155559999 
+Month: 12 
+Year: 2007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place order with very long input values</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on Place order button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Fill out form with valid dummy credentials
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Copy and paste each data 3 times in the provided field
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on purchase</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel order from checkout modal</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on Place order button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on close</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">User is returned to cart page. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORD-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that user is not able to click on the page while purchase confirmation message is displayed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on Place order button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Fill out form with valid dummy credentials
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on purchase
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. DO NOT CLOSE CONFIRMATION WINDOW
+5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click on purchase</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">User is not able to interact with the background or other fields until confirmation pop-up message is closed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is able to put multiple orders and is provided new and different Order ID every time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Module 6: Contact Form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONT-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONT-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONT-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONT-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONT-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONT-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONT-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONT-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONT-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Module 7: About Us</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About us</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB-09</t>
   </si>
 </sst>
 </file>
@@ -1967,12 +4194,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3988,7 +6215,7 @@
       <c r="H6" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="12" t="s">
         <v>112</v>
       </c>
       <c r="J6" s="11" t="s">
@@ -4318,7 +6545,7 @@
       <c r="M13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N13" s="24" t="s">
+      <c r="N13" s="23" t="s">
         <v>52</v>
       </c>
       <c r="O13" s="4"/>
@@ -4748,7 +6975,7 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="25.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
       <c r="B4" s="7" t="s">
         <v>4</v>
@@ -4820,7 +7047,7 @@
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="110" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -4834,12 +7061,24 @@
       <c r="G6" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+      <c r="H6" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="N6" s="18" t="s">
         <v>23</v>
       </c>
@@ -4853,26 +7092,38 @@
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="146.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>170</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
+        <v>176</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="N7" s="18" t="s">
         <v>23</v>
       </c>
@@ -4886,26 +7137,38 @@
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="97.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="10" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>170</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
+        <v>181</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="N8" s="18" t="s">
         <v>23</v>
       </c>
@@ -4919,26 +7182,38 @@
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
     </row>
-    <row r="9" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="134.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="10" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>170</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
+        <v>186</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="N9" s="18" t="s">
         <v>23</v>
       </c>
@@ -4952,26 +7227,38 @@
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="97.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="10" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>170</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
+        <v>190</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="N10" s="18" t="s">
         <v>23</v>
       </c>
@@ -4985,26 +7272,38 @@
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
     </row>
-    <row r="11" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="195.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="10" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>170</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
+        <v>195</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="N11" s="18" t="s">
         <v>23</v>
       </c>
@@ -5018,26 +7317,38 @@
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="69.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="10" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>170</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
+        <v>199</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="N12" s="20" t="s">
         <v>52</v>
       </c>
@@ -5051,27 +7362,41 @@
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
     </row>
-    <row r="13" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="172.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="10" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>170</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="20"/>
+        <v>205</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13" s="18" t="s">
+        <v>23</v>
+      </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
@@ -5082,25 +7407,41 @@
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="89.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="160.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="10" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="20"/>
+      <c r="G14" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="18" t="s">
+        <v>23</v>
+      </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
@@ -5116,7 +7457,16 @@
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
       <c r="J15" s="22"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
@@ -5132,6 +7482,16 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
@@ -5147,6 +7507,16 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
@@ -5161,6 +7531,17 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
@@ -5175,6 +7556,2141 @@
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="E3:N3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M6:M14" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N6:N14" type="list">
+      <formula1>"Not Run,Passed,Failed,Blocked"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" display=" https://www.demoblaze.com/"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:W1048576"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="35.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="21.14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="25.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="92.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="80.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="79.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="114.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="80.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="80.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="58.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="160.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="111.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N18" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="194.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="42.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="E3:N3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M6:M19" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N6:N19" type="list">
+      <formula1>"Not Run,Passed,Failed,Blocked"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" display=" https://www.demoblaze.com/"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:W1048576"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="35.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="21.14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="25.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="160.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="42.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="E3:N3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M6:M14" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N6:N14" type="list">
+      <formula1>"Not Run,Passed,Failed,Blocked"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" display=" https://www.demoblaze.com/"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:W1048576"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="35.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="21.14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="25.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="160.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="42.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>

--- a/docs/TestCases/Test_Cases.xlsx
+++ b/docs/TestCases/Test_Cases.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="358">
   <si>
     <t xml:space="preserve">Demoblaze Test Cases</t>
   </si>
@@ -3863,28 +3863,206 @@
     <t xml:space="preserve">Contact</t>
   </si>
   <si>
+    <t xml:space="preserve">Validate contact form with valid data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged in and on the homepage.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on contact from nav-bar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Input provided data in the fields
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on send message</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail: example@gmail.ch
+Name: Martin
+Message: Test!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmation message appears.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User receives a pop-up stating : „Thanks for the message!!“</t>
+  </si>
+  <si>
     <t xml:space="preserve">CONT-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Attempt sending contact message with empty email field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Name: Martin
+Message: Test!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error message or pop-up is displayed</t>
+  </si>
+  <si>
     <t xml:space="preserve">CONT-03</t>
   </si>
   <si>
+    <t xml:space="preserve">Attempt sending contact message with empty name field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail: example@gmail.ch
+Message: Test!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not clarified in documentation if anonymus messages are allowed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If anonymous messages are allowed, the message should be submitted successfully. Otherwise, an error message should be displayed.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CONT-04</t>
   </si>
   <si>
+    <t xml:space="preserve">Attempt sending contact message with empty message field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail: example@gmail.ch
+Name: Martin
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">CONT-05</t>
   </si>
   <si>
+    <t xml:space="preserve">Attempt sending a contact message with invalid e-mail format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail: abc
+Name: Martin
+Message: Test!</t>
+  </si>
+  <si>
     <t xml:space="preserve">CONT-06</t>
   </si>
   <si>
+    <t xml:space="preserve">Close contact submission form without sending the message
+(close button)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on contact from nav-bar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on close</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Submission form is closed. User is back to homepage</t>
+  </si>
+  <si>
     <t xml:space="preserve">CONT-07</t>
   </si>
   <si>
-    <t xml:space="preserve">CONT-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONT-09</t>
+    <t xml:space="preserve">Close contact submission form without sending the message
+(x button)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Click on contact from nav-bar
+2. Click on the “x” button</t>
   </si>
   <si>
     <t xml:space="preserve">Module 7: About Us</t>
@@ -3896,28 +4074,636 @@
     <t xml:space="preserve">About us</t>
   </si>
   <si>
+    <t xml:space="preserve">Open About us module</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on „About us“ from the nav-bar
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">About us module opens successfully</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About us opens the modal </t>
+  </si>
+  <si>
     <t xml:space="preserve">AB-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Verify embedded video is displayed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on „About us“ from the nav-bar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Observe if video is visible
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Video player is visible and inside the modal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video player is visible inside the modal</t>
+  </si>
+  <si>
     <t xml:space="preserve">AB-03</t>
   </si>
   <si>
+    <t xml:space="preserve">Play video</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on „About us“ from the nav-bar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on the play button
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Video starts playing</t>
+  </si>
+  <si>
     <t xml:space="preserve">AB-04</t>
   </si>
   <si>
+    <t xml:space="preserve">Pause video</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on „About us“ from the nav-bar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on the play button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on the video to pause
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Video pauses when pause is clicked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video paused successfully</t>
+  </si>
+  <si>
     <t xml:space="preserve">AB-05</t>
   </si>
   <si>
+    <t xml:space="preserve">Close video from integrated „X“ button</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on „About us“ from the nav-bar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on the integrated „X“ button to close the modal
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Modal closes and user is returned to homepage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modal is closed and user is landed on homepage</t>
+  </si>
+  <si>
     <t xml:space="preserve">AB-06</t>
   </si>
   <si>
+    <t xml:space="preserve">Close video by clicking outside</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on „About us“ from the nav-bar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click outside of the modal to close the video
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Modal should close when clicking outside the dialogue
+(Not specified in documentation)</t>
+  </si>
+  <si>
     <t xml:space="preserve">AB-07</t>
   </si>
   <si>
+    <t xml:space="preserve">Close video from integrated „Close“ button</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on „About us“ from the nav-bar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on the integrated „Close“ button to close the modal
+</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">AB-08</t>
   </si>
   <si>
+    <t xml:space="preserve">Attempt opening multiple about us modules</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on „About us“ from the nav-bar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on the integrated „X“ button to close the modal
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Repeat steps 1 and 2 multiple times
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Modal opens correctly every time without visual issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modal opens and closes without issues</t>
+  </si>
+  <si>
     <t xml:space="preserve">AB-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assert that full screen button works on video player</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on „About us“ from the nav-bar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on the play button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on the „Full Screen“ button in bottom right 
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Triggers video full screen on click</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video is presented in full screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assert that screemn in screen button works on video player</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on „About us“ from the nav-bar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on the play button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on the „Screen in screen“ button from video nav-bar
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Triggers video in bottom right corner outside of the modal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video is presented outside of the modal in the bottom right corner</t>
   </si>
 </sst>
 </file>
@@ -3927,7 +4713,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4018,6 +4804,14 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -4101,7 +4895,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4154,10 +4948,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4198,8 +4988,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -4696,7 +5494,7 @@
       <c r="M7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="N7" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O7" s="4"/>
@@ -4741,7 +5539,7 @@
       <c r="M8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N8" s="14" t="s">
+      <c r="N8" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O8" s="4"/>
@@ -4786,7 +5584,7 @@
       <c r="M9" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="N9" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O9" s="4"/>
@@ -4829,7 +5627,7 @@
       <c r="M10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N10" s="14" t="s">
+      <c r="N10" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O10" s="4"/>
@@ -4853,7 +5651,7 @@
       <c r="F11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>41</v>
       </c>
       <c r="H11" s="11" t="s">
@@ -4874,7 +5672,7 @@
       <c r="M11" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="14" t="s">
+      <c r="N11" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O11" s="4"/>
@@ -4919,7 +5717,7 @@
       <c r="M12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="14" t="s">
+      <c r="N12" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O12" s="4"/>
@@ -4964,7 +5762,7 @@
       <c r="M13" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N13" s="16" t="s">
+      <c r="N13" s="15" t="s">
         <v>52</v>
       </c>
       <c r="O13" s="4"/>
@@ -4982,7 +5780,7 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="17"/>
+      <c r="E14" s="16"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -5007,7 +5805,7 @@
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="17"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -5351,7 +6149,7 @@
       <c r="M6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="18" t="s">
+      <c r="N6" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O6" s="4"/>
@@ -5396,7 +6194,7 @@
       <c r="M7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="N7" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O7" s="4"/>
@@ -5441,7 +6239,7 @@
       <c r="M8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N8" s="14" t="s">
+      <c r="N8" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O8" s="4"/>
@@ -5486,7 +6284,7 @@
       <c r="M9" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="N9" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O9" s="4"/>
@@ -5531,7 +6329,7 @@
       <c r="M10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N10" s="16" t="s">
+      <c r="N10" s="15" t="s">
         <v>52</v>
       </c>
       <c r="O10" s="4"/>
@@ -5576,7 +6374,7 @@
       <c r="M11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="14" t="s">
+      <c r="N11" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O11" s="4"/>
@@ -5619,7 +6417,7 @@
       <c r="M12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N12" s="14" t="s">
+      <c r="N12" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O12" s="4"/>
@@ -5658,13 +6456,13 @@
       <c r="K13" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="18" t="s">
         <v>83</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N13" s="20" t="s">
+      <c r="N13" s="19" t="s">
         <v>52</v>
       </c>
       <c r="O13" s="4"/>
@@ -5697,7 +6495,7 @@
       <c r="I14" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="20" t="s">
         <v>86</v>
       </c>
       <c r="K14" s="11" t="s">
@@ -5709,7 +6507,7 @@
       <c r="M14" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N14" s="20" t="s">
+      <c r="N14" s="19" t="s">
         <v>52</v>
       </c>
       <c r="O14" s="4"/>
@@ -5752,7 +6550,7 @@
       <c r="M15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="14" t="s">
+      <c r="N15" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O15" s="4"/>
@@ -5795,7 +6593,7 @@
       <c r="M16" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N16" s="14" t="s">
+      <c r="N16" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O16" s="4"/>
@@ -5838,7 +6636,7 @@
       <c r="M17" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N17" s="14" t="s">
+      <c r="N17" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O17" s="4"/>
@@ -5881,7 +6679,7 @@
       <c r="M18" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N18" s="14" t="s">
+      <c r="N18" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O18" s="4"/>
@@ -5899,7 +6697,7 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
-      <c r="J19" s="22"/>
+      <c r="J19" s="21"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
@@ -6230,7 +7028,7 @@
       <c r="M6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="18" t="s">
+      <c r="N6" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O6" s="4"/>
@@ -6275,7 +7073,7 @@
       <c r="M7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="18" t="s">
+      <c r="N7" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O7" s="4"/>
@@ -6320,7 +7118,7 @@
       <c r="M8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="18" t="s">
+      <c r="N8" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O8" s="4"/>
@@ -6365,7 +7163,7 @@
       <c r="M9" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="18" t="s">
+      <c r="N9" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O9" s="4"/>
@@ -6410,7 +7208,7 @@
       <c r="M10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N10" s="18" t="s">
+      <c r="N10" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O10" s="4"/>
@@ -6455,7 +7253,7 @@
       <c r="M11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="18" t="s">
+      <c r="N11" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O11" s="4"/>
@@ -6500,7 +7298,7 @@
       <c r="M12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N12" s="18" t="s">
+      <c r="N12" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O12" s="4"/>
@@ -6539,13 +7337,13 @@
       <c r="K13" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="18" t="s">
         <v>147</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N13" s="23" t="s">
+      <c r="N13" s="22" t="s">
         <v>52</v>
       </c>
       <c r="O13" s="4"/>
@@ -6590,7 +7388,7 @@
       <c r="M14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="18" t="s">
+      <c r="N14" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O14" s="4"/>
@@ -6635,7 +7433,7 @@
       <c r="M15" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N15" s="18" t="s">
+      <c r="N15" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O15" s="4"/>
@@ -6680,7 +7478,7 @@
       <c r="M16" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="N16" s="18" t="s">
+      <c r="N16" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O16" s="4"/>
@@ -6725,7 +7523,7 @@
       <c r="M17" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N17" s="14" t="s">
+      <c r="N17" s="13" t="s">
         <v>23</v>
       </c>
       <c r="O17" s="4"/>
@@ -6743,7 +7541,7 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="J18" s="22"/>
+      <c r="J18" s="21"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
@@ -6975,7 +7773,7 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="25.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
       <c r="B4" s="7" t="s">
         <v>4</v>
@@ -7047,7 +7845,7 @@
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="110" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -7079,7 +7877,7 @@
       <c r="M6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="18" t="s">
+      <c r="N6" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O6" s="4"/>
@@ -7092,7 +7890,7 @@
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="146.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -7124,7 +7922,7 @@
       <c r="M7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="18" t="s">
+      <c r="N7" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O7" s="4"/>
@@ -7137,7 +7935,7 @@
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
     </row>
-    <row r="8" customFormat="false" ht="97.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -7169,7 +7967,7 @@
       <c r="M8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N8" s="18" t="s">
+      <c r="N8" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O8" s="4"/>
@@ -7182,7 +7980,7 @@
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
     </row>
-    <row r="9" customFormat="false" ht="134.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -7214,7 +8012,7 @@
       <c r="M9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="18" t="s">
+      <c r="N9" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O9" s="4"/>
@@ -7227,7 +8025,7 @@
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="97.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -7259,7 +8057,7 @@
       <c r="M10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N10" s="18" t="s">
+      <c r="N10" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O10" s="4"/>
@@ -7304,7 +8102,7 @@
       <c r="M11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="18" t="s">
+      <c r="N11" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O11" s="4"/>
@@ -7349,7 +8147,7 @@
       <c r="M12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="20" t="s">
+      <c r="N12" s="19" t="s">
         <v>52</v>
       </c>
       <c r="O12" s="4"/>
@@ -7394,7 +8192,7 @@
       <c r="M13" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N13" s="18" t="s">
+      <c r="N13" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O13" s="4"/>
@@ -7439,7 +8237,7 @@
       <c r="M14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="18" t="s">
+      <c r="N14" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O14" s="4"/>
@@ -7457,16 +8255,16 @@
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="24"/>
+      <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="22"/>
+      <c r="J15" s="21"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
@@ -7482,7 +8280,7 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="24"/>
+      <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -7490,8 +8288,8 @@
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
@@ -7507,7 +8305,7 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="24"/>
+      <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -7515,8 +8313,8 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
@@ -7531,8 +8329,8 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -7540,8 +8338,8 @@
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
@@ -7556,8 +8354,8 @@
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -7565,8 +8363,8 @@
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
@@ -7739,7 +8537,7 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="25.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
       <c r="B4" s="7" t="s">
         <v>4</v>
@@ -7811,7 +8609,7 @@
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="92.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -7843,7 +8641,7 @@
       <c r="M6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="18" t="s">
+      <c r="N6" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O6" s="4"/>
@@ -7856,7 +8654,7 @@
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -7888,7 +8686,7 @@
       <c r="M7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="23" t="s">
+      <c r="N7" s="22" t="s">
         <v>52</v>
       </c>
       <c r="O7" s="4"/>
@@ -7901,7 +8699,7 @@
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
     </row>
-    <row r="8" customFormat="false" ht="80.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -7933,7 +8731,7 @@
       <c r="M8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N8" s="18" t="s">
+      <c r="N8" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O8" s="4"/>
@@ -7946,7 +8744,7 @@
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
     </row>
-    <row r="9" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -7978,7 +8776,7 @@
       <c r="M9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="23" t="s">
+      <c r="N9" s="22" t="s">
         <v>52</v>
       </c>
       <c r="O9" s="4"/>
@@ -7991,7 +8789,7 @@
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="79.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -8023,7 +8821,7 @@
       <c r="M10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N10" s="23" t="s">
+      <c r="N10" s="22" t="s">
         <v>52</v>
       </c>
       <c r="O10" s="4"/>
@@ -8036,7 +8834,7 @@
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
     </row>
-    <row r="11" customFormat="false" ht="114.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -8068,7 +8866,7 @@
       <c r="M11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="18" t="s">
+      <c r="N11" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O11" s="4"/>
@@ -8081,7 +8879,7 @@
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="80.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -8113,7 +8911,7 @@
       <c r="M12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="20" t="s">
+      <c r="N12" s="19" t="s">
         <v>52</v>
       </c>
       <c r="O12" s="4"/>
@@ -8126,7 +8924,7 @@
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
     </row>
-    <row r="13" customFormat="false" ht="80.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -8158,7 +8956,7 @@
       <c r="M13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N13" s="20" t="s">
+      <c r="N13" s="19" t="s">
         <v>52</v>
       </c>
       <c r="O13" s="4"/>
@@ -8201,7 +8999,7 @@
       <c r="M14" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N14" s="18" t="s">
+      <c r="N14" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O14" s="4"/>
@@ -8246,7 +9044,7 @@
       <c r="M15" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N15" s="23" t="s">
+      <c r="N15" s="22" t="s">
         <v>52</v>
       </c>
       <c r="O15" s="4"/>
@@ -8259,7 +9057,7 @@
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -8291,7 +9089,7 @@
       <c r="M16" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N16" s="23" t="s">
+      <c r="N16" s="22" t="s">
         <v>52</v>
       </c>
       <c r="O16" s="4"/>
@@ -8304,7 +9102,7 @@
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
     </row>
-    <row r="17" customFormat="false" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -8336,7 +9134,7 @@
       <c r="M17" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N17" s="23" t="s">
+      <c r="N17" s="22" t="s">
         <v>52</v>
       </c>
       <c r="O17" s="4"/>
@@ -8353,7 +9151,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="24"/>
+      <c r="D18" s="4"/>
       <c r="E18" s="10" t="s">
         <v>270</v>
       </c>
@@ -8379,7 +9177,7 @@
       <c r="M18" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="N18" s="18" t="s">
+      <c r="N18" s="17" t="s">
         <v>23</v>
       </c>
       <c r="O18" s="4"/>
@@ -8396,7 +9194,7 @@
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="24"/>
+      <c r="D19" s="4"/>
       <c r="E19" s="10" t="s">
         <v>274</v>
       </c>
@@ -8424,7 +9222,7 @@
       <c r="M19" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N19" s="23" t="s">
+      <c r="N19" s="22" t="s">
         <v>52</v>
       </c>
       <c r="O19" s="4"/>
@@ -8441,8 +9239,8 @@
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -8450,8 +9248,8 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
@@ -8623,7 +9421,7 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="25.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
       <c r="B4" s="7" t="s">
         <v>4</v>
@@ -8695,7 +9493,7 @@
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -8706,14 +9504,30 @@
       <c r="F6" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="18"/>
+      <c r="G6" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>23</v>
+      </c>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
@@ -8724,25 +9538,41 @@
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="10" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="18"/>
+      <c r="G7" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="22" t="s">
+        <v>52</v>
+      </c>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
@@ -8753,25 +9583,41 @@
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="10" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="18"/>
+      <c r="G8" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>23</v>
+      </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
@@ -8782,25 +9628,41 @@
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="10" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="18"/>
+      <c r="G9" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>23</v>
+      </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
@@ -8811,25 +9673,41 @@
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="10" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="18"/>
+      <c r="G10" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="22" t="s">
+        <v>52</v>
+      </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
@@ -8840,25 +9718,39 @@
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="10" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
+      <c r="G11" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>305</v>
+      </c>
       <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="18"/>
+      <c r="K11" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>23</v>
+      </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
@@ -8869,25 +9761,39 @@
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="10" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
+      <c r="G12" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>309</v>
+      </c>
       <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="20"/>
+      <c r="K12" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>23</v>
+      </c>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
@@ -8903,20 +9809,16 @@
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="18"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
@@ -8927,25 +9829,21 @@
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="160.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="18"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
@@ -8956,21 +9854,21 @@
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="42.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="24"/>
+      <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="22"/>
+      <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
@@ -8985,17 +9883,6 @@
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
@@ -9010,17 +9897,6 @@
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
@@ -9031,84 +9907,10 @@
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
-    </row>
-    <row r="19" customFormat="false" ht="42.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
-    </row>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -9120,17 +9922,20 @@
     <mergeCell ref="E3:N3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M6:M14" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M6:M12" type="list">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N6:N14" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N6:N12" type="list">
       <formula1>"Not Run,Passed,Failed,Blocked"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" display=" https://www.demoblaze.com/"/>
+    <hyperlink ref="J6" r:id="rId2" display="E-mail: example@gmail.ch&#10;Name: Martin&#10;Message: Test!"/>
+    <hyperlink ref="J8" r:id="rId3" display="E-mail: example@gmail.ch&#10;&#10;Message: Test!"/>
+    <hyperlink ref="J9" r:id="rId4" display="E-mail: example@gmail.ch&#10;Name: Martin&#10;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9151,8 +9956,10 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="23.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="35.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30.7"/>
@@ -9191,18 +9998,18 @@
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="5" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="4" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -9212,46 +10019,38 @@
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="6" t="s">
-        <v>290</v>
-      </c>
+      <c r="B3" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="25.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
-      <c r="B4" s="7" t="s">
-        <v>4</v>
-      </c>
+      <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -9266,347 +10065,455 @@
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="5" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="E5" s="8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="N5" s="8" t="s">
         <v>14</v>
       </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="6" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>292</v>
+      <c r="B6" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>314</v>
       </c>
       <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="18"/>
+      <c r="H6" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="7" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>292</v>
+      <c r="B7" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>319</v>
       </c>
       <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="18"/>
+      <c r="H7" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="8" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>292</v>
+      <c r="B8" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>324</v>
       </c>
       <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="18"/>
+      <c r="H8" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="9" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>292</v>
+      <c r="B9" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>328</v>
       </c>
       <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="18"/>
+      <c r="H9" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="10" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>292</v>
+      <c r="B10" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>333</v>
       </c>
       <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="18"/>
+      <c r="H10" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="11" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>292</v>
+      <c r="B11" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>338</v>
       </c>
       <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="18"/>
+      <c r="H11" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="12" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>292</v>
+      <c r="B12" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>342</v>
       </c>
       <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="20"/>
+      <c r="H12" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="13" customFormat="false" ht="160.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>292</v>
+      <c r="B13" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>345</v>
       </c>
       <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="18"/>
+      <c r="H13" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="160.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="14" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>292</v>
+      <c r="B14" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>350</v>
       </c>
       <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="18"/>
+      <c r="H14" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="15" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="4"/>
+      <c r="B15" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>23</v>
+      </c>
       <c r="L15" s="4"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="24"/>
+      <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -9614,24 +10521,21 @@
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="24"/>
+      <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -9639,24 +10543,20 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="18" customFormat="false" ht="42.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
+      <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -9664,93 +10564,98 @@
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
-    </row>
-    <row r="19" customFormat="false" ht="42.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G19" s="24"/>
+      <c r="J19" s="0"/>
+      <c r="K19" s="0"/>
       <c r="L19" s="4"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
+      <c r="G20" s="24"/>
+      <c r="J20" s="0"/>
+      <c r="K20" s="0"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
-    </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="G21" s="24"/>
+      <c r="J21" s="0"/>
+      <c r="K21" s="0"/>
+      <c r="L21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G22" s="24"/>
+      <c r="J22" s="0"/>
+      <c r="K22" s="0"/>
+      <c r="L22" s="0"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G23" s="24"/>
+      <c r="J23" s="0"/>
+      <c r="K23" s="0"/>
+      <c r="L23" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G24" s="24"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G25" s="24"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G26" s="25"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G27" s="24"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G28" s="24"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G29" s="24"/>
+    </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:W1"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M6:M14" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J6:J15" type="list">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N6:N14" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K6:K15" type="list">
       <formula1>"Not Run,Passed,Failed,Blocked"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" display=" https://www.demoblaze.com/"/>
+    <hyperlink ref="E2" r:id="rId1" display=" https://www.demoblaze.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
